--- a/artfynd/A 14627-2026 artfynd.xlsx
+++ b/artfynd/A 14627-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,61 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96896797</v>
+        <v>97404633</v>
       </c>
       <c r="B2" t="n">
-        <v>58003</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102125</v>
+        <v>1588</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SO Suolajärvet, Sikträsket, Lu lm</t>
+          <t>V Malmberget, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>740549</v>
+        <v>740544</v>
       </c>
       <c r="R2" t="n">
-        <v>7461628</v>
+        <v>7461541</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-09</t>
+          <t>2021-10-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-09</t>
+          <t>2021-10-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Åke Aronson</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Åke Aronson</t>
+          <t>Otilia Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97404651</v>
+        <v>97404634</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740241.6654689329</v>
+        <v>740431</v>
       </c>
       <c r="R3" t="n">
-        <v>7461553.70409149</v>
+        <v>7461537</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -855,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,16 +872,11 @@
         <v>97404635</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -937,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740431.4823517494</v>
+        <v>740431</v>
       </c>
       <c r="R4" t="n">
-        <v>7461541.453945085</v>
+        <v>7461541</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -970,19 +937,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97404626</v>
+        <v>97404628</v>
       </c>
       <c r="B5" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740533.7585918182</v>
+        <v>740277</v>
       </c>
       <c r="R5" t="n">
-        <v>7462086.503210257</v>
+        <v>7462207</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1082,19 +1034,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97404625</v>
+        <v>96896797</v>
       </c>
       <c r="B6" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1137,37 +1074,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>102125</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>V Malmberget, Lu lm</t>
+          <t>SO Suolajärvet, Sikträsket, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740663.1968702385</v>
+        <v>740549</v>
       </c>
       <c r="R6" t="n">
-        <v>7462102.420452481</v>
+        <v>7461628</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,22 +1136,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,49 +1156,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Åke Aronson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Otilia Johansson</t>
+          <t>Åke Aronson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97404633</v>
+        <v>97404625</v>
       </c>
       <c r="B7" t="n">
-        <v>89557</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1588</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1273,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740543.6630410454</v>
+        <v>740663</v>
       </c>
       <c r="R7" t="n">
-        <v>7461540.982539799</v>
+        <v>7462102</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1306,19 +1236,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,15 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97404634</v>
+        <v>97404626</v>
       </c>
       <c r="B8" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,21 +1276,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1385,10 +1300,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>740430.7711793726</v>
+        <v>740534</v>
       </c>
       <c r="R8" t="n">
-        <v>7461536.315860843</v>
+        <v>7462086</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1418,19 +1333,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,12 +1365,7 @@
         <v>97404629</v>
       </c>
       <c r="B9" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>740322.4373154314</v>
+        <v>740322</v>
       </c>
       <c r="R9" t="n">
-        <v>7462029.684130628</v>
+        <v>7462030</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1530,19 +1430,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,6 +1456,200 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>97404651</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>V Malmberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>740242</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7461554</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-10-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-10-12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>97404632</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>V Malmberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>740444</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7461675</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-10-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-10-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Otilia Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14627-2026 artfynd.xlsx
+++ b/artfynd/A 14627-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97404633</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97404634</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97404635</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97404628</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96896797</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97404625</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97404626</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97404629</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1553,6 +1598,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97404651</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1650,8 +1700,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97404632</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>